--- a/nilai-nilai/gti-2026/GTI_PAIK6404_2025_2_C.xlsx
+++ b/nilai-nilai/gti-2026/GTI_PAIK6404_2025_2_C.xlsx
@@ -1,141 +1,50 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10916"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macbook-undip/Documents/KULIAH/KAMPUS LAIN-LAIN/UTS dan UAS/Genap 2526/3_GTI_15/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A56D3A99-8777-6543-93EE-8C145F4706A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
+    <sheet name="Worksheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
-  <si>
-    <t>Mata Kuliah</t>
-  </si>
-  <si>
-    <t>: PAIK6404 - Grafika dan Komputasi Visual</t>
-  </si>
-  <si>
-    <t>Tahun Ajaran</t>
-  </si>
-  <si>
-    <t>: 2025</t>
-  </si>
-  <si>
-    <t>NDk5MjQ2</t>
-  </si>
-  <si>
-    <t>Semester</t>
-  </si>
-  <si>
-    <t>: Genap</t>
-  </si>
-  <si>
-    <t>Kelas</t>
-  </si>
-  <si>
-    <t>: C</t>
-  </si>
-  <si>
-    <t>Prodi</t>
-  </si>
-  <si>
-    <t>: S1-TEKNIK INFORMATIKA</t>
-  </si>
-  <si>
-    <t>NIM</t>
-  </si>
-  <si>
-    <t>Nama Mahasiswa</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Nilai Aktivitas Partisipatif (0,00-100,00) (10%)</t>
-  </si>
-  <si>
-    <t>Nilai Hasil Proyek (0,00-100,00) (40%)</t>
-  </si>
-  <si>
-    <t>Nilai Tugas (0,00-100,00) (5%)</t>
-  </si>
-  <si>
-    <t>Nilai Quiz (0,00-100,00) (5%)</t>
-  </si>
-  <si>
-    <t>Nilai UTS (0,00-100,00) (20%)</t>
-  </si>
-  <si>
-    <t>Nilai UAS (0,00-100) (20%)</t>
-  </si>
-  <si>
-    <t>Nilai Akhir Angka (0,00-100,00)</t>
-  </si>
-  <si>
-    <t>Nilai Akhir Huruf (A/B/C/D/E)</t>
-  </si>
-  <si>
-    <t>Nilai Bobot (0-4)</t>
-  </si>
-  <si>
-    <t>24060121130059</t>
-  </si>
-  <si>
-    <t>AHMAD DANUN HANANI</t>
-  </si>
-  <si>
-    <t>ULANG</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
+      <name val="Calibri"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -150,27 +59,90 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
-      <protection locked="0"/>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -460,144 +432,204 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:M8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="57.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="45.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="35.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="31.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="37.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="35.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="21.1640625" bestFit="1" customWidth="1"/>
+    <col width="17.5" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="49.33203125" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="10.5" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="8.1640625" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="57.6640625" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="45.83203125" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="36.5" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="35.33203125" bestFit="1" customWidth="1" min="8" max="9"/>
+    <col width="31.6640625" bestFit="1" customWidth="1" min="10" max="10"/>
+    <col width="37.6640625" bestFit="1" customWidth="1" min="11" max="11"/>
+    <col width="35.33203125" bestFit="1" customWidth="1" min="12" max="12"/>
+    <col width="21.1640625" bestFit="1" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Mata Kuliah</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>: PAIK6404 - Grafika dan Komputasi Visual</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>4</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Tahun Ajaran</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>: 2025</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>NDk5MjQ2</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Semester</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>: Genap</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Kelas</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>: C</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Prodi</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>: S1-TEKNIK INFORMATIKA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NIM</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Nama Mahasiswa</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Semester</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Nilai Aktivitas Partisipatif (0,00-100,00) (10%)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nilai Hasil Proyek (0,00-100,00) (40%)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Nilai Tugas (0,00-100,00) (5%)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Nilai Quiz (0,00-100,00) (5%)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Nilai UTS (0,00-100,00) (20%)</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Nilai UAS (0,00-100) (20%)</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Nilai Akhir Angka (0,00-100,00)</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Nilai Akhir Huruf (A/B/C/D/E)</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Nilai Bobot (0-4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>24060121130059</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>AHMAD DANUN HANANI</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I7" t="s">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ULANG</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="H8" s="3" t="n"/>
+      <c r="I8" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="J7" t="s">
-        <v>19</v>
-      </c>
-      <c r="K7" t="s">
-        <v>20</v>
-      </c>
-      <c r="L7" t="s">
-        <v>21</v>
-      </c>
-      <c r="M7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8">
-        <v>10</v>
-      </c>
-      <c r="D8" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3">
-        <v>18</v>
-      </c>
-      <c r="J8" s="3"/>
+      <c r="J8" s="3" t="n"/>
       <c r="K8" s="2">
         <f>ROUND( ((E8*10+F8*40+G8*5+H8*5+I8*20+J8*20) / 100), 2)</f>
-        <v>3.6</v>
-      </c>
-      <c r="L8" s="2" t="str">
+        <v/>
+      </c>
+      <c r="L8" s="2">
         <f>IF(AND(K8&gt;=80, K8&lt;=100), "A", IF(AND(K8&gt;=70, K8&lt;=79.99999999999), "B", IF(AND(K8&gt;=60, K8&lt;=69.9999999999), "C", IF(AND(K8&gt;=51, K8&lt;=59.999999999), "D", IF(AND(K8&gt;=0, K8&lt;=50.999999999), "E",  "E"  )  )  )  )  )</f>
-        <v>E</v>
-      </c>
-      <c r="M8" t="str">
+        <v/>
+      </c>
+      <c r="M8">
         <f>IF(AND(K8&gt;=80, K8&lt;=100), "4", IF(AND(K8&gt;=70, K8&lt;=79.99999999999), "3", IF(AND(K8&gt;=60, K8&lt;=69.9999999999), "2", IF(AND(K8&gt;=51, K8&lt;=59.999999999), "1", IF(AND(K8&gt;=0, K8&lt;=50.999999999), "0",  "0"  )  )  )  )  )</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="0" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
 </worksheet>

--- a/nilai-nilai/gti-2026/GTI_PAIK6404_2025_2_C.xlsx
+++ b/nilai-nilai/gti-2026/GTI_PAIK6404_2025_2_C.xlsx
@@ -34,7 +34,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -44,6 +44,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFD7BE"/>
       </patternFill>
     </fill>
   </fills>
@@ -59,7 +64,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -67,6 +72,10 @@
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -607,7 +616,7 @@
       </c>
       <c r="E8" s="3" t="n"/>
       <c r="F8" s="3" t="n"/>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="5" t="n">
         <v>60</v>
       </c>
       <c r="H8" s="3" t="n"/>
